--- a/public/exports-from-60-with-coowners/19438414.xlsx
+++ b/public/exports-from-60-with-coowners/19438414.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024939</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304440</t>
+          <t xml:space="preserve">311304591</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">

--- a/public/exports-from-60-with-coowners/19438414.xlsx
+++ b/public/exports-from-60-with-coowners/19438414.xlsx
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024939</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123772</t>
+          <t xml:space="preserve">311123773</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123772</t>
+          <t xml:space="preserve">311123773</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10654,12 +10654,12 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10729,12 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10804,12 +10804,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10879,12 +10879,12 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10954,12 +10954,12 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11104,12 +11104,12 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11179,12 +11179,12 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11254,12 +11254,12 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11329,12 +11329,12 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11404,12 +11404,12 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11554,12 +11554,12 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11629,12 +11629,12 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11704,12 +11704,12 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11779,12 +11779,12 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11854,12 +11854,12 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11929,12 +11929,12 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12004,12 +12004,12 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12079,12 +12079,12 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12154,12 +12154,12 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12229,12 +12229,12 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12304,12 +12304,12 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -25564,7 +25564,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304591</t>
+          <t xml:space="preserve">311304440</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">

--- a/public/exports-from-60-with-coowners/19438414.xlsx
+++ b/public/exports-from-60-with-coowners/19438414.xlsx
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123773</t>
+          <t xml:space="preserve">311123772</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123773</t>
+          <t xml:space="preserve">311123772</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -12379,12 +12379,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12529,12 +12529,12 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12679,12 +12679,12 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12754,12 +12754,12 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12829,12 +12829,12 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12904,12 +12904,12 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12979,12 +12979,12 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13054,12 +13054,12 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13129,12 +13129,12 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13204,12 +13204,12 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13279,12 +13279,12 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13354,12 +13354,12 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
